--- a/artfynd/A 5462-2024 artfynd.xlsx
+++ b/artfynd/A 5462-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120513465</v>
+        <v>120514784</v>
       </c>
       <c r="B2" t="n">
-        <v>77479</v>
+        <v>74654</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534196</v>
+        <v>534242</v>
       </c>
       <c r="R2" t="n">
-        <v>6744723</v>
+        <v>6744844</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120514784</v>
+        <v>120513465</v>
       </c>
       <c r="B3" t="n">
-        <v>74654</v>
+        <v>77479</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534242</v>
+        <v>534196</v>
       </c>
       <c r="R3" t="n">
-        <v>6744844</v>
+        <v>6744723</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,6 +876,867 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120533383</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90506</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kölmyrorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>534265</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6744763</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jakob Wallin, Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120513531</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Messmörstenen, Messmörstenen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>534222</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6744700</v>
+      </c>
+      <c r="S5" t="n">
+        <v>9</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Anna-Britt Olsson, Lisa Olson, Rolf Lundqvist, Göran Ehn, Nicklas Gustavsson, Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120515860</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Messmörstenen, Messmörstenen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>534339</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6744506</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Anna-Britt Olsson, Lisa Olson, Rolf Lundqvist, Göran Ehn, Nicklas Gustavsson, Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120515642</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Messmörstenen, Messmörstenen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>534296</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6744609</v>
+      </c>
+      <c r="S7" t="n">
+        <v>9</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Anna-Britt Olsson, Lisa Olson, Rolf Lundqvist, Göran Ehn, Nicklas Gustavsson, Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120533388</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kölmyrorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>534169</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6744793</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jakob Wallin, Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120533382</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kölmyrorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>534219</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6744701</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jakob Wallin, Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120533384</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kölmyrorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>534222</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6744719</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jakob Wallin, Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120533387</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8432</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kölmyrorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>534149</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6744904</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jakob Wallin, Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5462-2024 artfynd.xlsx
+++ b/artfynd/A 5462-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120514784</v>
+        <v>120513465</v>
       </c>
       <c r="B2" t="n">
-        <v>74654</v>
+        <v>77479</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534242</v>
+        <v>534196</v>
       </c>
       <c r="R2" t="n">
-        <v>6744844</v>
+        <v>6744723</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120513465</v>
+        <v>120514784</v>
       </c>
       <c r="B3" t="n">
-        <v>77479</v>
+        <v>74654</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534196</v>
+        <v>534242</v>
       </c>
       <c r="R3" t="n">
-        <v>6744723</v>
+        <v>6744844</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120533383</v>
+        <v>120533387</v>
       </c>
       <c r="B4" t="n">
-        <v>90506</v>
+        <v>8432</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3242</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534265</v>
+        <v>534149</v>
       </c>
       <c r="R4" t="n">
-        <v>6744763</v>
+        <v>6744904</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1332,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120533388</v>
+        <v>120533384</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534169</v>
+        <v>534222</v>
       </c>
       <c r="R8" t="n">
-        <v>6744793</v>
+        <v>6744719</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1434,7 +1434,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120533382</v>
+        <v>120533388</v>
       </c>
       <c r="B9" t="n">
         <v>78542</v>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534219</v>
+        <v>534169</v>
       </c>
       <c r="R9" t="n">
-        <v>6744701</v>
+        <v>6744793</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120533384</v>
+        <v>120533383</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>90506</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534222</v>
+        <v>534265</v>
       </c>
       <c r="R10" t="n">
-        <v>6744719</v>
+        <v>6744763</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120533387</v>
+        <v>120533382</v>
       </c>
       <c r="B11" t="n">
-        <v>8432</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,25 +1650,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534149</v>
+        <v>534219</v>
       </c>
       <c r="R11" t="n">
-        <v>6744904</v>
+        <v>6744701</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 5462-2024 artfynd.xlsx
+++ b/artfynd/A 5462-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1738,6 +1738,130 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120515789</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Messmörstenen, Messmörstenen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>534410</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6744565</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5462-2024 artfynd.xlsx
+++ b/artfynd/A 5462-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120513465</v>
+        <v>120533383</v>
       </c>
       <c r="B2" t="n">
-        <v>77531</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>3242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Messmörstenen, Dlr</t>
+          <t>Kölmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534196</v>
+        <v>534265</v>
       </c>
       <c r="R2" t="n">
-        <v>6744723</v>
+        <v>6744763</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Bo karlstens</t>
+          <t>Jakob Wallin, Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120514784</v>
+        <v>120515786</v>
       </c>
       <c r="B3" t="n">
-        <v>74702</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534242</v>
+        <v>534375</v>
       </c>
       <c r="R3" t="n">
-        <v>6744844</v>
+        <v>6744504</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,9 +840,19 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120533384</v>
+        <v>120515789</v>
       </c>
       <c r="B4" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +890,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kölmyrorna, Dlr</t>
+          <t>Messmörstenen, Messmörstenen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534222</v>
+        <v>534410</v>
       </c>
       <c r="R4" t="n">
-        <v>6744719</v>
+        <v>6744565</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,29 +958,40 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Nicklas Gustavsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -984,16 +1001,11 @@
         <v>120513531</v>
       </c>
       <c r="B5" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1098,53 +1110,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120533387</v>
+        <v>120515642</v>
       </c>
       <c r="B6" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kölmyrorna, Dlr</t>
+          <t>Messmörstenen, Messmörstenen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534149</v>
+        <v>534296</v>
       </c>
       <c r="R6" t="n">
-        <v>6744904</v>
+        <v>6744609</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,9 +1178,24 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,31 +1210,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Nicklas Gustavsson</t>
+          <t>Bo karlstens, Anna-Britt Olsson, Lisa Olson, Rolf Lundqvist, Göran Ehn, Nicklas Gustavsson, Jakob Wallin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120515642</v>
+        <v>120515860</v>
       </c>
       <c r="B7" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1240,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534296</v>
+        <v>534339</v>
       </c>
       <c r="R7" t="n">
-        <v>6744609</v>
+        <v>6744506</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1275,7 +1292,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1285,12 +1302,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,37 +1334,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120533383</v>
+        <v>120533382</v>
       </c>
       <c r="B8" t="n">
-        <v>90605</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534265</v>
+        <v>534219</v>
       </c>
       <c r="R8" t="n">
-        <v>6744763</v>
+        <v>6744701</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1419,19 +1431,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120533388</v>
+        <v>120533384</v>
       </c>
       <c r="B9" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1459,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534169</v>
+        <v>534222</v>
       </c>
       <c r="R9" t="n">
-        <v>6744793</v>
+        <v>6744719</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1521,19 +1528,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120515860</v>
+        <v>120533388</v>
       </c>
       <c r="B10" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1557,17 +1559,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Messmörstenen, Messmörstenen, Dlr</t>
+          <t>Kölmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534339</v>
+        <v>534169</v>
       </c>
       <c r="R10" t="n">
-        <v>6744506</v>
+        <v>6744793</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1594,24 +1596,9 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,27 +1613,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Britt Olsson, Lisa Olson, Rolf Lundqvist, Göran Ehn, Nicklas Gustavsson, Jakob Wallin</t>
+          <t>Jakob Wallin, Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120533382</v>
+        <v>120514784</v>
       </c>
       <c r="B11" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,37 +1636,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kölmyrorna, Dlr</t>
+          <t>Messmörstenen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534219</v>
+        <v>534242</v>
       </c>
       <c r="R11" t="n">
-        <v>6744701</v>
+        <v>6744844</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1728,27 +1710,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Nicklas Gustavsson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120515789</v>
+        <v>120533387</v>
       </c>
       <c r="B12" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,48 +1733,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Messmörstenen, Messmörstenen, Dlr</t>
+          <t>Kölmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534410</v>
+        <v>534149</v>
       </c>
       <c r="R12" t="n">
-        <v>6744565</v>
+        <v>6744904</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1824,77 +1790,61 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Jakob Wallin, Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120516117</v>
+        <v>120513465</v>
       </c>
       <c r="B13" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>228579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1904,13 +1854,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534375</v>
+        <v>534196</v>
       </c>
       <c r="R13" t="n">
-        <v>6744504</v>
+        <v>6744723</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1937,19 +1887,9 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,12 +1904,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Nicklas Gustavsson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 5462-2024 artfynd.xlsx
+++ b/artfynd/A 5462-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533383</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120515786</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120515789</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513531</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120515642</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120515860</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533382</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1525,6 +1565,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533384</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1622,6 +1667,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533388</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1719,6 +1769,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120514784</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1816,6 +1871,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533387</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1913,8 +1973,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513465</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>